--- a/artfynd/A 44656-2023 artfynd.xlsx
+++ b/artfynd/A 44656-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44656-2023 artfynd.xlsx
+++ b/artfynd/A 44656-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>112802466</v>
       </c>
       <c r="B2" t="n">
-        <v>56753</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>112793940</v>
       </c>
       <c r="B3" t="n">
-        <v>56753</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -829,14 +829,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bultbodfloten-Sälgtjärnbäcken (Bultbodfloten-Sälgtjärnbäcken), Dlr</t>
+          <t>Bultbodfloten-Sälgtjärnbäcken, Bultbodfloten-Sälgtjärnbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>475033</v>
       </c>
       <c r="R3" t="n">
-        <v>6805620</v>
+        <v>6805621</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -913,7 +913,7 @@
         <v>112802385</v>
       </c>
       <c r="B4" t="n">
-        <v>56753</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>112793807</v>
       </c>
       <c r="B5" t="n">
-        <v>56753</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bultbodfloten-Sälgtjärnbäcken (Bultbodfloten-Sälgtjärnbäcken), Dlr</t>
+          <t>Bultbodfloten-Sälgtjärnbäcken, Bultbodfloten-Sälgtjärnbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">

--- a/artfynd/A 44656-2023 artfynd.xlsx
+++ b/artfynd/A 44656-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>112802466</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>112793940</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>112802385</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>112793807</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
